--- a/data/Monster.xlsx
+++ b/data/Monster.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,46 @@
           <t>designer</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>critchance</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>speed</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>exp_reward</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>gold_reward</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +479,46 @@
           <t>int32</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -449,6 +529,58 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>designer</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>击杀该怪给予的经验</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>击杀该怪给予的金币</t>
         </is>
       </c>
     </row>
@@ -456,80 +588,464 @@
       <c r="A6" t="n">
         <v>1</v>
       </c>
+      <c r="C6" t="n">
+        <v>180</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>2</v>
       </c>
+      <c r="C7" t="n">
+        <v>220</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>3</v>
       </c>
+      <c r="C8" t="n">
+        <v>260</v>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>4</v>
       </c>
+      <c r="C9" t="n">
+        <v>300</v>
+      </c>
+      <c r="D9" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>5</v>
       </c>
+      <c r="C10" t="n">
+        <v>350</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>6</v>
       </c>
+      <c r="C11" t="n">
+        <v>500</v>
+      </c>
+      <c r="D11" t="n">
+        <v>22</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="n">
+        <v>80</v>
+      </c>
+      <c r="J11" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>7</v>
       </c>
+      <c r="C12" t="n">
+        <v>650</v>
+      </c>
+      <c r="D12" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>8</v>
       </c>
+      <c r="C13" t="n">
+        <v>800</v>
+      </c>
+      <c r="D13" t="n">
+        <v>28</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I13" t="n">
+        <v>130</v>
+      </c>
+      <c r="J13" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>9</v>
       </c>
+      <c r="C14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>14</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15</v>
+      </c>
+      <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" t="n">
+        <v>160</v>
+      </c>
+      <c r="J14" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>10</v>
       </c>
+      <c r="C15" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D15" t="n">
+        <v>34</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" t="n">
+        <v>20</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="n">
+        <v>14</v>
+      </c>
+      <c r="I15" t="n">
+        <v>200</v>
+      </c>
+      <c r="J15" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>11</v>
       </c>
+      <c r="C16" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D16" t="n">
+        <v>38</v>
+      </c>
+      <c r="E16" t="n">
+        <v>18</v>
+      </c>
+      <c r="F16" t="n">
+        <v>20</v>
+      </c>
+      <c r="G16" t="n">
+        <v>15</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" t="n">
+        <v>260</v>
+      </c>
+      <c r="J16" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>12</v>
       </c>
+      <c r="C17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>42</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" t="n">
+        <v>25</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" t="n">
+        <v>320</v>
+      </c>
+      <c r="J17" t="n">
+        <v>190</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>13</v>
       </c>
+      <c r="C18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D18" t="n">
+        <v>46</v>
+      </c>
+      <c r="E18" t="n">
+        <v>22</v>
+      </c>
+      <c r="F18" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>16</v>
+      </c>
+      <c r="I18" t="n">
+        <v>400</v>
+      </c>
+      <c r="J18" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>14</v>
       </c>
+      <c r="C19" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D19" t="n">
+        <v>52</v>
+      </c>
+      <c r="E19" t="n">
+        <v>25</v>
+      </c>
+      <c r="F19" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H19" t="n">
+        <v>17</v>
+      </c>
+      <c r="I19" t="n">
+        <v>520</v>
+      </c>
+      <c r="J19" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>15</v>
       </c>
+      <c r="C20" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>60</v>
+      </c>
+      <c r="E20" t="n">
+        <v>28</v>
+      </c>
+      <c r="F20" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" t="n">
+        <v>18</v>
+      </c>
+      <c r="I20" t="n">
+        <v>680</v>
+      </c>
+      <c r="J20" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>80</v>
+      </c>
+      <c r="E21" t="n">
+        <v>35</v>
+      </c>
+      <c r="F21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G21" t="n">
+        <v>25</v>
+      </c>
+      <c r="H21" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J21" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/data/Monster.xlsx
+++ b/data/Monster.xlsx
@@ -428,30 +428,10 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>designer</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="n">
         <v>1</v>

--- a/data/Monster.xlsx
+++ b/data/Monster.xlsx
@@ -468,9 +468,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
@@ -483,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>180</v>
+        <v>380</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -498,7 +495,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I6" t="n">
         <v>20</v>
@@ -512,10 +509,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>220</v>
+        <v>380</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
@@ -527,7 +524,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I7" t="n">
         <v>25</v>
@@ -541,10 +538,10 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>3040</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
@@ -556,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="I8" t="n">
         <v>30</v>
@@ -570,10 +567,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>4090</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
@@ -585,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
@@ -599,10 +596,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>350</v>
+        <v>5570</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="E10" t="n">
         <v>7</v>
@@ -614,7 +611,7 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="I10" t="n">
         <v>50</v>
@@ -628,10 +625,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>500</v>
+        <v>6540</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>178</v>
       </c>
       <c r="E11" t="n">
         <v>8</v>
@@ -643,7 +640,7 @@
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="I11" t="n">
         <v>80</v>
@@ -657,10 +654,10 @@
         <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>650</v>
+        <v>7670</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>211</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
@@ -672,7 +669,7 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
@@ -686,10 +683,10 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>800</v>
+        <v>9100</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>260</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -701,7 +698,7 @@
         <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="I13" t="n">
         <v>130</v>
@@ -715,10 +712,10 @@
         <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>1000</v>
+        <v>10830</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>301</v>
       </c>
       <c r="E14" t="n">
         <v>14</v>
@@ -730,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="I14" t="n">
         <v>160</v>
@@ -744,10 +741,10 @@
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>1300</v>
+        <v>11940</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>350</v>
       </c>
       <c r="E15" t="n">
         <v>16</v>
@@ -759,7 +756,7 @@
         <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="I15" t="n">
         <v>200</v>
@@ -773,10 +770,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>1600</v>
+        <v>14190</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>407</v>
       </c>
       <c r="E16" t="n">
         <v>18</v>
@@ -788,7 +785,7 @@
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>15</v>
+        <v>142</v>
       </c>
       <c r="I16" t="n">
         <v>260</v>
@@ -802,10 +799,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>2000</v>
+        <v>14940</v>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>448</v>
       </c>
       <c r="E17" t="n">
         <v>20</v>
@@ -817,7 +814,7 @@
         <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="I17" t="n">
         <v>320</v>
@@ -831,10 +828,10 @@
         <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>2500</v>
+        <v>17520</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>529</v>
       </c>
       <c r="E18" t="n">
         <v>22</v>
@@ -846,7 +843,7 @@
         <v>15</v>
       </c>
       <c r="H18" t="n">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c r="I18" t="n">
         <v>400</v>
@@ -860,10 +857,10 @@
         <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>3200</v>
+        <v>18870</v>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>603</v>
       </c>
       <c r="E19" t="n">
         <v>25</v>
@@ -875,7 +872,7 @@
         <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>17</v>
+        <v>204</v>
       </c>
       <c r="I19" t="n">
         <v>520</v>
@@ -889,10 +886,10 @@
         <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>4000</v>
+        <v>22260</v>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>709</v>
       </c>
       <c r="E20" t="n">
         <v>28</v>
@@ -904,7 +901,7 @@
         <v>20</v>
       </c>
       <c r="H20" t="n">
-        <v>18</v>
+        <v>239</v>
       </c>
       <c r="I20" t="n">
         <v>680</v>
@@ -918,10 +915,10 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>6000</v>
+        <v>50720</v>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>686</v>
       </c>
       <c r="E21" t="n">
         <v>35</v>
@@ -933,7 +930,7 @@
         <v>25</v>
       </c>
       <c r="H21" t="n">
-        <v>20</v>
+        <v>185</v>
       </c>
       <c r="I21" t="n">
         <v>1200</v>
